--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（subCL）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（subCL）参数校验测试用例.xlsx
@@ -95,14 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attachCL，subCLFullName指定的cl不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL，subCLFullName指定的cl为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建主表t1
 2、将test子表挂载到t1主表，其中test子表在sdb不存在
 3、检查执行结果</t>
@@ -117,16 +109,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>attachCL，指定有效区间范围挂载子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、挂载成功，执行db.snapshot(8)查看cl挂载成功，分区等信息展示正确
 2、对主表插入数据，插入成功，数据录入正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL，指定无效区间范围挂载子表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -167,10 +151,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>detachCL，subCLFullName指定的cl不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>挂载失败，提示CL不存在，提示信息合理准确</t>
   </si>
   <si>
@@ -178,10 +158,6 @@
   </si>
   <si>
     <t>去挂载子表失败，提示参数错误，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>detachCL，subCLFullName取值为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -199,6 +175,24 @@
   b.db.testCS.t1.detachCL("test")，输入子表时没有指定CS
 3、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attachCL，subCLFullName指定的cl不存在_st.verify.subCL.001</t>
+  </si>
+  <si>
+    <t>attachCL，subCLFullName指定的cl为空_st.verify.subCL.002</t>
+  </si>
+  <si>
+    <t>attachCL，指定有效区间范围挂载子表_st.verify.subCL.003</t>
+  </si>
+  <si>
+    <t>attachCL，指定无效区间范围挂载子表_st.verify.subCL.004</t>
+  </si>
+  <si>
+    <t>detachCL，subCLFullName指定的cl不存在_st.verify.subCL.005</t>
+  </si>
+  <si>
+    <t>detachCL，subCLFullName取值为空_st.verify.subCL.006</t>
   </si>
 </sst>
 </file>
@@ -740,10 +734,10 @@
     </row>
     <row r="3" spans="1:9" ht="175.5">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
@@ -758,10 +752,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -769,96 +763,136 @@
     </row>
     <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="175.5">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="108">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="108">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="94.5">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2"/>
